--- a/30_テスト/31_ユースケース記述テスト仕様書.xlsx
+++ b/30_テスト/31_ユースケース記述テスト仕様書.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\s_sakagami\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="762" documentId="13_ncr:1_{BBBAFD8D-438D-42AC-9D14-DDE72FBA6E8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FFE7FE05-EEC7-420F-B55E-70E819ADBB86}"/>
+  <xr:revisionPtr revIDLastSave="779" documentId="13_ncr:1_{BBBAFD8D-438D-42AC-9D14-DDE72FBA6E8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0FEE2787-DC6E-4AA3-818D-244C9311E7F7}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="379" uniqueCount="255">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="385" uniqueCount="258">
   <si>
     <t>ユースケース記述テスト仕様書</t>
   </si>
@@ -310,7 +310,16 @@
     <t>建物情報を登録</t>
   </si>
   <si>
+    <t>ログイン状態で新しい建物を入力しで次へボタンをクリックする</t>
+  </si>
+  <si>
     <t>入力した建物情報が保存される</t>
+  </si>
+  <si>
+    <t>登録されている建物と重複した名前を入れたまま次へボタンをクリックする</t>
+  </si>
+  <si>
+    <t>「入力された建物名が保存されている建物名と重複しています」とメッセージを表示し画面遷移を中断</t>
   </si>
   <si>
     <t>被害状況入力</t>
@@ -513,7 +522,8 @@
     <t>分析処理中にネットワークを切断またはタイムアウトさせる</t>
   </si>
   <si>
-    <t>エラーメッセージが表示され、被害状況入力画面または再試行画面へ安全に戻ります</t>
+    <t>決められた制限時間内に分析が完了しなかった場合
+処理を中断し、エラーメッセージと戻るボタンを表示する</t>
   </si>
   <si>
     <t>追加質問のリンクを表示する</t>
@@ -1555,7 +1565,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M80"/>
+  <dimension ref="A1:M81"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="4.140625" style="2" bestFit="1" customWidth="1"/>
@@ -1964,10 +1974,10 @@
         <v>63</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H15" s="5"/>
       <c r="I15" s="5"/>
@@ -1976,21 +1986,21 @@
       <c r="L15" s="5"/>
       <c r="M15" s="5"/>
     </row>
-    <row r="16" spans="1:13" s="3" customFormat="1" ht="15" customHeight="1">
+    <row r="16" spans="1:13" s="3" customFormat="1" ht="27">
       <c r="A16" s="4">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>65</v>
+        <v>47</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>48</v>
+        <v>62</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="F16" s="6" t="s">
         <v>66</v>
@@ -2005,27 +2015,27 @@
       <c r="L16" s="5"/>
       <c r="M16" s="5"/>
     </row>
-    <row r="17" spans="1:13" s="3" customFormat="1" ht="29.25" customHeight="1">
+    <row r="17" spans="1:13" s="3" customFormat="1" ht="15" customHeight="1">
       <c r="A17" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B17" s="5" t="s">
         <v>68</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>69</v>
+        <v>48</v>
       </c>
       <c r="D17" s="5" t="s">
         <v>27</v>
       </c>
       <c r="E17" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="F17" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="G17" s="6" t="s">
         <v>70</v>
-      </c>
-      <c r="F17" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="G17" s="6" t="s">
-        <v>72</v>
       </c>
       <c r="H17" s="5"/>
       <c r="I17" s="5"/>
@@ -2034,15 +2044,15 @@
       <c r="L17" s="5"/>
       <c r="M17" s="5"/>
     </row>
-    <row r="18" spans="1:13" s="3" customFormat="1" ht="16.5" customHeight="1">
+    <row r="18" spans="1:13" s="3" customFormat="1" ht="29.25" customHeight="1">
       <c r="A18" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="D18" s="5" t="s">
         <v>27</v>
@@ -2065,25 +2075,25 @@
     </row>
     <row r="19" spans="1:13" s="3" customFormat="1" ht="16.5" customHeight="1">
       <c r="A19" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="C19" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="E19" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="D19" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="E19" s="6" t="s">
+      <c r="F19" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="F19" s="6" t="s">
+      <c r="G19" s="6" t="s">
         <v>78</v>
-      </c>
-      <c r="G19" s="6" t="s">
-        <v>79</v>
       </c>
       <c r="H19" s="5"/>
       <c r="I19" s="5"/>
@@ -2094,25 +2104,25 @@
     </row>
     <row r="20" spans="1:13" s="3" customFormat="1" ht="16.5" customHeight="1">
       <c r="A20" s="4">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D20" s="5" t="s">
         <v>31</v>
       </c>
       <c r="E20" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="F20" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="F20" s="6" t="s">
+      <c r="G20" s="6" t="s">
         <v>82</v>
-      </c>
-      <c r="G20" s="6" t="s">
-        <v>83</v>
       </c>
       <c r="H20" s="5"/>
       <c r="I20" s="5"/>
@@ -2121,15 +2131,15 @@
       <c r="L20" s="5"/>
       <c r="M20" s="5"/>
     </row>
-    <row r="21" spans="1:13" s="3" customFormat="1" ht="31.5" customHeight="1">
+    <row r="21" spans="1:13" s="3" customFormat="1" ht="16.5" customHeight="1">
       <c r="A21" s="4">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>52</v>
+        <v>83</v>
       </c>
       <c r="D21" s="5" t="s">
         <v>31</v>
@@ -2150,12 +2160,12 @@
       <c r="L21" s="5"/>
       <c r="M21" s="5"/>
     </row>
-    <row r="22" spans="1:13" s="3" customFormat="1" ht="16.5" customHeight="1">
+    <row r="22" spans="1:13" s="3" customFormat="1" ht="31.5" customHeight="1">
       <c r="A22" s="4">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="C22" s="5" t="s">
         <v>52</v>
@@ -2181,25 +2191,25 @@
     </row>
     <row r="23" spans="1:13" s="3" customFormat="1" ht="16.5" customHeight="1">
       <c r="A23" s="4">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>90</v>
+        <v>52</v>
       </c>
       <c r="D23" s="5" t="s">
         <v>31</v>
       </c>
       <c r="E23" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="F23" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="F23" s="6" t="s">
+      <c r="G23" s="6" t="s">
         <v>92</v>
-      </c>
-      <c r="G23" s="6" t="s">
-        <v>93</v>
       </c>
       <c r="H23" s="5"/>
       <c r="I23" s="5"/>
@@ -2210,25 +2220,25 @@
     </row>
     <row r="24" spans="1:13" s="3" customFormat="1" ht="16.5" customHeight="1">
       <c r="A24" s="4">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>69</v>
+        <v>93</v>
       </c>
       <c r="D24" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="E24" s="6" t="s">
         <v>94</v>
       </c>
-      <c r="E24" s="6" t="s">
+      <c r="F24" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="F24" s="6" t="s">
+      <c r="G24" s="6" t="s">
         <v>96</v>
-      </c>
-      <c r="G24" s="6" t="s">
-        <v>97</v>
       </c>
       <c r="H24" s="5"/>
       <c r="I24" s="5"/>
@@ -2239,25 +2249,25 @@
     </row>
     <row r="25" spans="1:13" s="3" customFormat="1" ht="16.5" customHeight="1">
       <c r="A25" s="4">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="C25" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="D25" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="E25" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="D25" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="E25" s="6" t="s">
+      <c r="F25" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="F25" s="6" t="s">
+      <c r="G25" s="6" t="s">
         <v>100</v>
-      </c>
-      <c r="G25" s="6" t="s">
-        <v>101</v>
       </c>
       <c r="H25" s="5"/>
       <c r="I25" s="5"/>
@@ -2266,27 +2276,27 @@
       <c r="L25" s="5"/>
       <c r="M25" s="5"/>
     </row>
-    <row r="26" spans="1:13" s="3" customFormat="1" ht="31.5" customHeight="1">
+    <row r="26" spans="1:13" s="3" customFormat="1" ht="16.5" customHeight="1">
       <c r="A26" s="4">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="C26" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="D26" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="E26" s="6" t="s">
         <v>102</v>
       </c>
-      <c r="D26" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="E26" s="6" t="s">
+      <c r="F26" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="F26" s="6" t="s">
+      <c r="G26" s="6" t="s">
         <v>104</v>
-      </c>
-      <c r="G26" s="6" t="s">
-        <v>105</v>
       </c>
       <c r="H26" s="5"/>
       <c r="I26" s="5"/>
@@ -2295,27 +2305,27 @@
       <c r="L26" s="5"/>
       <c r="M26" s="5"/>
     </row>
-    <row r="27" spans="1:13" s="3" customFormat="1" ht="30.75" customHeight="1">
+    <row r="27" spans="1:13" s="3" customFormat="1" ht="31.5" customHeight="1">
       <c r="A27" s="4">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D27" s="5" t="s">
         <v>31</v>
       </c>
       <c r="E27" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="F27" s="6" t="s">
         <v>107</v>
       </c>
-      <c r="F27" s="6" t="s">
+      <c r="G27" s="6" t="s">
         <v>108</v>
-      </c>
-      <c r="G27" s="6" t="s">
-        <v>109</v>
       </c>
       <c r="H27" s="5"/>
       <c r="I27" s="5"/>
@@ -2324,18 +2334,18 @@
       <c r="L27" s="5"/>
       <c r="M27" s="5"/>
     </row>
-    <row r="28" spans="1:13" s="3" customFormat="1" ht="15" customHeight="1">
+    <row r="28" spans="1:13" s="3" customFormat="1" ht="30.75" customHeight="1">
       <c r="A28" s="4">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>21</v>
+        <v>109</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>56</v>
+        <v>31</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>110</v>
@@ -2353,18 +2363,18 @@
       <c r="L28" s="5"/>
       <c r="M28" s="5"/>
     </row>
-    <row r="29" spans="1:13" s="3" customFormat="1" ht="32.25" customHeight="1">
+    <row r="29" spans="1:13" s="3" customFormat="1" ht="15" customHeight="1">
       <c r="A29" s="4">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>102</v>
+        <v>21</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>27</v>
+        <v>56</v>
       </c>
       <c r="E29" s="6" t="s">
         <v>113</v>
@@ -2382,27 +2392,27 @@
       <c r="L29" s="5"/>
       <c r="M29" s="5"/>
     </row>
-    <row r="30" spans="1:13" s="3" customFormat="1" ht="15" customHeight="1">
+    <row r="30" spans="1:13" s="3" customFormat="1" ht="32.25" customHeight="1">
       <c r="A30" s="4">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>116</v>
-      </c>
-      <c r="C30" s="6" t="s">
-        <v>117</v>
+        <v>71</v>
+      </c>
+      <c r="C30" s="5" t="s">
+        <v>105</v>
       </c>
       <c r="D30" s="5" t="s">
         <v>27</v>
       </c>
       <c r="E30" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="F30" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="G30" s="6" t="s">
         <v>118</v>
-      </c>
-      <c r="F30" s="6" t="s">
-        <v>119</v>
-      </c>
-      <c r="G30" s="6" t="s">
-        <v>120</v>
       </c>
       <c r="H30" s="5"/>
       <c r="I30" s="5"/>
@@ -2413,25 +2423,25 @@
     </row>
     <row r="31" spans="1:13" s="3" customFormat="1" ht="15" customHeight="1">
       <c r="A31" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>21</v>
+        <v>120</v>
       </c>
       <c r="D31" s="5" t="s">
         <v>27</v>
       </c>
       <c r="E31" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="F31" s="6" t="s">
         <v>122</v>
       </c>
-      <c r="F31" s="6" t="s">
+      <c r="G31" s="6" t="s">
         <v>123</v>
-      </c>
-      <c r="G31" s="6" t="s">
-        <v>124</v>
       </c>
       <c r="H31" s="5"/>
       <c r="I31" s="5"/>
@@ -2440,27 +2450,27 @@
       <c r="L31" s="5"/>
       <c r="M31" s="5"/>
     </row>
-    <row r="32" spans="1:13" s="3" customFormat="1" ht="27">
+    <row r="32" spans="1:13" s="3" customFormat="1" ht="15" customHeight="1">
       <c r="A32" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="C32" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D32" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="E32" s="6" t="s">
         <v>125</v>
       </c>
-      <c r="D32" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="E32" s="6" t="s">
+      <c r="F32" s="6" t="s">
         <v>126</v>
       </c>
-      <c r="F32" s="6" t="s">
+      <c r="G32" s="6" t="s">
         <v>127</v>
-      </c>
-      <c r="G32" s="6" t="s">
-        <v>128</v>
       </c>
       <c r="H32" s="5"/>
       <c r="I32" s="5"/>
@@ -2469,18 +2479,18 @@
       <c r="L32" s="5"/>
       <c r="M32" s="5"/>
     </row>
-    <row r="33" spans="1:13" s="3" customFormat="1" ht="15" customHeight="1">
+    <row r="33" spans="1:13" s="3" customFormat="1" ht="27">
       <c r="A33" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>21</v>
+        <v>128</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="E33" s="6" t="s">
         <v>129</v>
@@ -2500,25 +2510,25 @@
     </row>
     <row r="34" spans="1:13" s="3" customFormat="1" ht="15" customHeight="1">
       <c r="A34" s="4">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>133</v>
+        <v>21</v>
       </c>
       <c r="D34" s="5" t="s">
         <v>27</v>
       </c>
       <c r="E34" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="F34" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="G34" s="6" t="s">
         <v>134</v>
-      </c>
-      <c r="F34" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="G34" s="6" t="s">
-        <v>136</v>
       </c>
       <c r="H34" s="5"/>
       <c r="I34" s="5"/>
@@ -2529,25 +2539,25 @@
     </row>
     <row r="35" spans="1:13" s="3" customFormat="1" ht="15" customHeight="1">
       <c r="A35" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="D35" s="5" t="s">
         <v>27</v>
       </c>
       <c r="E35" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="F35" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="G35" s="6" t="s">
         <v>139</v>
-      </c>
-      <c r="F35" s="6" t="s">
-        <v>140</v>
-      </c>
-      <c r="G35" s="6" t="s">
-        <v>141</v>
       </c>
       <c r="H35" s="5"/>
       <c r="I35" s="5"/>
@@ -2558,25 +2568,25 @@
     </row>
     <row r="36" spans="1:13" s="3" customFormat="1" ht="15" customHeight="1">
       <c r="A36" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="C36" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="D36" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="E36" s="6" t="s">
         <v>142</v>
       </c>
-      <c r="D36" s="5" t="s">
+      <c r="F36" s="6" t="s">
         <v>143</v>
       </c>
-      <c r="E36" s="6" t="s">
+      <c r="G36" s="6" t="s">
         <v>144</v>
-      </c>
-      <c r="F36" s="6" t="s">
-        <v>145</v>
-      </c>
-      <c r="G36" s="6" t="s">
-        <v>146</v>
       </c>
       <c r="H36" s="5"/>
       <c r="I36" s="5"/>
@@ -2585,27 +2595,27 @@
       <c r="L36" s="5"/>
       <c r="M36" s="5"/>
     </row>
-    <row r="37" spans="1:13" s="3" customFormat="1" ht="31.5" customHeight="1">
+    <row r="37" spans="1:13" s="3" customFormat="1" ht="15" customHeight="1">
       <c r="A37" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B37" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="C37" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="D37" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="E37" s="6" t="s">
         <v>147</v>
       </c>
-      <c r="C37" s="5" t="s">
+      <c r="F37" s="6" t="s">
         <v>148</v>
       </c>
-      <c r="D37" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="E37" s="6" t="s">
+      <c r="G37" s="6" t="s">
         <v>149</v>
-      </c>
-      <c r="F37" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="G37" s="6" t="s">
-        <v>151</v>
       </c>
       <c r="H37" s="5"/>
       <c r="I37" s="5"/>
@@ -2614,27 +2624,27 @@
       <c r="L37" s="5"/>
       <c r="M37" s="5"/>
     </row>
-    <row r="38" spans="1:13" s="3" customFormat="1" ht="14.25" customHeight="1">
+    <row r="38" spans="1:13" s="3" customFormat="1" ht="31.5" customHeight="1">
       <c r="A38" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>133</v>
+        <v>151</v>
       </c>
       <c r="D38" s="5" t="s">
         <v>27</v>
       </c>
       <c r="E38" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="F38" s="6" t="s">
         <v>153</v>
       </c>
-      <c r="F38" s="6" t="s">
+      <c r="G38" s="6" t="s">
         <v>154</v>
-      </c>
-      <c r="G38" s="6" t="s">
-        <v>155</v>
       </c>
       <c r="H38" s="5"/>
       <c r="I38" s="5"/>
@@ -2645,25 +2655,25 @@
     </row>
     <row r="39" spans="1:13" s="3" customFormat="1" ht="14.25" customHeight="1">
       <c r="A39" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="C39" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="D39" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="E39" s="6" t="s">
         <v>156</v>
       </c>
-      <c r="D39" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="E39" s="6" t="s">
+      <c r="F39" s="6" t="s">
         <v>157</v>
       </c>
-      <c r="F39" s="6" t="s">
+      <c r="G39" s="6" t="s">
         <v>158</v>
-      </c>
-      <c r="G39" s="6" t="s">
-        <v>159</v>
       </c>
       <c r="H39" s="5"/>
       <c r="I39" s="5"/>
@@ -2674,25 +2684,25 @@
     </row>
     <row r="40" spans="1:13" s="3" customFormat="1" ht="14.25" customHeight="1">
       <c r="A40" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="C40" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="D40" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="E40" s="6" t="s">
         <v>160</v>
       </c>
-      <c r="D40" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="E40" s="6" t="s">
+      <c r="F40" s="6" t="s">
         <v>161</v>
       </c>
-      <c r="F40" s="6" t="s">
+      <c r="G40" s="6" t="s">
         <v>162</v>
-      </c>
-      <c r="G40" s="6" t="s">
-        <v>163</v>
       </c>
       <c r="H40" s="5"/>
       <c r="I40" s="5"/>
@@ -2701,27 +2711,27 @@
       <c r="L40" s="5"/>
       <c r="M40" s="5"/>
     </row>
-    <row r="41" spans="1:13" s="3" customFormat="1" ht="15" customHeight="1">
+    <row r="41" spans="1:13" s="3" customFormat="1" ht="14.25" customHeight="1">
       <c r="A41" s="4">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B41" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="C41" s="5" t="s">
+        <v>163</v>
+      </c>
+      <c r="D41" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="E41" s="6" t="s">
         <v>164</v>
       </c>
-      <c r="C41" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="D41" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="E41" s="6" t="s">
+      <c r="F41" s="6" t="s">
         <v>165</v>
       </c>
-      <c r="F41" s="6" t="s">
+      <c r="G41" s="6" t="s">
         <v>166</v>
-      </c>
-      <c r="G41" s="6" t="s">
-        <v>167</v>
       </c>
       <c r="H41" s="5"/>
       <c r="I41" s="5"/>
@@ -2735,7 +2745,7 @@
         <v>1</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C42" s="5" t="s">
         <v>48</v>
@@ -2743,14 +2753,14 @@
       <c r="D42" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="E42" s="5" t="s">
+      <c r="E42" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="F42" s="6" t="s">
         <v>169</v>
       </c>
-      <c r="F42" s="5" t="s">
+      <c r="G42" s="6" t="s">
         <v>170</v>
-      </c>
-      <c r="G42" s="6" t="s">
-        <v>171</v>
       </c>
       <c r="H42" s="5"/>
       <c r="I42" s="5"/>
@@ -2761,25 +2771,25 @@
     </row>
     <row r="43" spans="1:13" s="3" customFormat="1" ht="15" customHeight="1">
       <c r="A43" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B43" s="5" t="s">
+        <v>171</v>
+      </c>
+      <c r="C43" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="D43" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="E43" s="5" t="s">
         <v>172</v>
       </c>
-      <c r="C43" s="5" t="s">
+      <c r="F43" s="5" t="s">
         <v>173</v>
       </c>
-      <c r="D43" s="5" t="s">
+      <c r="G43" s="6" t="s">
         <v>174</v>
-      </c>
-      <c r="E43" s="5" t="s">
-        <v>175</v>
-      </c>
-      <c r="F43" s="5" t="s">
-        <v>176</v>
-      </c>
-      <c r="G43" s="6" t="s">
-        <v>177</v>
       </c>
       <c r="H43" s="5"/>
       <c r="I43" s="5"/>
@@ -2790,25 +2800,25 @@
     </row>
     <row r="44" spans="1:13" s="3" customFormat="1" ht="15" customHeight="1">
       <c r="A44" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="C44" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="D44" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="E44" s="5" t="s">
         <v>178</v>
       </c>
-      <c r="D44" s="5" t="s">
-        <v>174</v>
-      </c>
-      <c r="E44" s="5" t="s">
+      <c r="F44" s="5" t="s">
         <v>179</v>
       </c>
-      <c r="F44" s="5" t="s">
+      <c r="G44" s="6" t="s">
         <v>180</v>
-      </c>
-      <c r="G44" s="6" t="s">
-        <v>181</v>
       </c>
       <c r="H44" s="5"/>
       <c r="I44" s="5"/>
@@ -2817,27 +2827,27 @@
       <c r="L44" s="5"/>
       <c r="M44" s="5"/>
     </row>
-    <row r="45" spans="1:13" s="3" customFormat="1" ht="27">
+    <row r="45" spans="1:13" s="3" customFormat="1" ht="15" customHeight="1">
       <c r="A45" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B45" s="5" t="s">
+        <v>175</v>
+      </c>
+      <c r="C45" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="D45" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="E45" s="5" t="s">
         <v>182</v>
       </c>
-      <c r="C45" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="D45" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="E45" s="5" t="s">
+      <c r="F45" s="5" t="s">
         <v>183</v>
       </c>
-      <c r="F45" s="5" t="s">
+      <c r="G45" s="6" t="s">
         <v>184</v>
-      </c>
-      <c r="G45" s="6" t="s">
-        <v>185</v>
       </c>
       <c r="H45" s="5"/>
       <c r="I45" s="5"/>
@@ -2846,27 +2856,27 @@
       <c r="L45" s="5"/>
       <c r="M45" s="5"/>
     </row>
-    <row r="46" spans="1:13" s="3" customFormat="1" ht="13.5">
+    <row r="46" spans="1:13" s="3" customFormat="1" ht="27">
       <c r="A46" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>21</v>
+        <v>48</v>
       </c>
       <c r="D46" s="5" t="s">
         <v>27</v>
       </c>
       <c r="E46" s="5" t="s">
+        <v>186</v>
+      </c>
+      <c r="F46" s="5" t="s">
         <v>187</v>
       </c>
-      <c r="F46" s="5" t="s">
+      <c r="G46" s="6" t="s">
         <v>188</v>
-      </c>
-      <c r="G46" s="6" t="s">
-        <v>189</v>
       </c>
       <c r="H46" s="5"/>
       <c r="I46" s="5"/>
@@ -2875,27 +2885,27 @@
       <c r="L46" s="5"/>
       <c r="M46" s="5"/>
     </row>
-    <row r="47" spans="1:13" s="3" customFormat="1" ht="15" customHeight="1">
+    <row r="47" spans="1:13" s="3" customFormat="1" ht="13.5">
       <c r="A47" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>48</v>
+        <v>21</v>
       </c>
       <c r="D47" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="E47" s="6" t="s">
+      <c r="E47" s="5" t="s">
+        <v>190</v>
+      </c>
+      <c r="F47" s="5" t="s">
         <v>191</v>
       </c>
-      <c r="F47" s="6" t="s">
+      <c r="G47" s="6" t="s">
         <v>192</v>
-      </c>
-      <c r="G47" s="6" t="s">
-        <v>193</v>
       </c>
       <c r="H47" s="5"/>
       <c r="I47" s="5"/>
@@ -2906,25 +2916,25 @@
     </row>
     <row r="48" spans="1:13" s="3" customFormat="1" ht="15" customHeight="1">
       <c r="A48" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>195</v>
+        <v>48</v>
       </c>
       <c r="D48" s="5" t="s">
         <v>27</v>
       </c>
       <c r="E48" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="F48" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="G48" s="6" t="s">
         <v>196</v>
-      </c>
-      <c r="F48" s="6" t="s">
-        <v>197</v>
-      </c>
-      <c r="G48" s="6" t="s">
-        <v>198</v>
       </c>
       <c r="H48" s="5"/>
       <c r="I48" s="5"/>
@@ -2933,18 +2943,18 @@
       <c r="L48" s="5"/>
       <c r="M48" s="5"/>
     </row>
-    <row r="49" spans="1:13" s="3" customFormat="1" ht="32.25" customHeight="1">
+    <row r="49" spans="1:13" s="3" customFormat="1" ht="15" customHeight="1">
       <c r="A49" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>52</v>
+        <v>198</v>
       </c>
       <c r="D49" s="5" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="E49" s="6" t="s">
         <v>199</v>
@@ -2962,27 +2972,27 @@
       <c r="L49" s="5"/>
       <c r="M49" s="5"/>
     </row>
-    <row r="50" spans="1:13" s="3" customFormat="1" ht="15.75" customHeight="1">
+    <row r="50" spans="1:13" s="3" customFormat="1" ht="32.25" customHeight="1">
       <c r="A50" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="D50" s="5" t="s">
-        <v>56</v>
+        <v>31</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>110</v>
+        <v>202</v>
       </c>
       <c r="F50" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="H50" s="5"/>
       <c r="I50" s="5"/>
@@ -2991,27 +3001,27 @@
       <c r="L50" s="5"/>
       <c r="M50" s="5"/>
     </row>
-    <row r="51" spans="1:13" s="3" customFormat="1" ht="15" customHeight="1">
+    <row r="51" spans="1:13" s="3" customFormat="1" ht="15.75" customHeight="1">
       <c r="A51" s="4">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>204</v>
+        <v>21</v>
       </c>
       <c r="D51" s="5" t="s">
-        <v>21</v>
+        <v>56</v>
       </c>
       <c r="E51" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="F51" s="6" t="s">
         <v>205</v>
       </c>
-      <c r="F51" s="6" t="s">
+      <c r="G51" s="6" t="s">
         <v>206</v>
-      </c>
-      <c r="G51" s="6" t="s">
-        <v>207</v>
       </c>
       <c r="H51" s="5"/>
       <c r="I51" s="5"/>
@@ -3020,27 +3030,27 @@
       <c r="L51" s="5"/>
       <c r="M51" s="5"/>
     </row>
-    <row r="52" spans="1:13" s="3" customFormat="1" ht="30.75" customHeight="1">
+    <row r="52" spans="1:13" s="3" customFormat="1" ht="15" customHeight="1">
       <c r="A52" s="4">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="C52" s="5" t="s">
+        <v>207</v>
+      </c>
+      <c r="D52" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E52" s="6" t="s">
         <v>208</v>
       </c>
-      <c r="D52" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="E52" s="6" t="s">
+      <c r="F52" s="6" t="s">
         <v>209</v>
       </c>
-      <c r="F52" s="6" t="s">
+      <c r="G52" s="6" t="s">
         <v>210</v>
-      </c>
-      <c r="G52" s="6" t="s">
-        <v>211</v>
       </c>
       <c r="H52" s="5"/>
       <c r="I52" s="5"/>
@@ -3049,27 +3059,27 @@
       <c r="L52" s="5"/>
       <c r="M52" s="5"/>
     </row>
-    <row r="53" spans="1:13" s="3" customFormat="1" ht="15" customHeight="1">
+    <row r="53" spans="1:13" s="3" customFormat="1" ht="30.75" customHeight="1">
       <c r="A53" s="4">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="B53" s="5" t="s">
+        <v>197</v>
+      </c>
+      <c r="C53" s="5" t="s">
+        <v>211</v>
+      </c>
+      <c r="D53" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="E53" s="6" t="s">
         <v>212</v>
       </c>
-      <c r="C53" s="5" t="s">
+      <c r="F53" s="6" t="s">
         <v>213</v>
       </c>
-      <c r="D53" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="E53" s="6" t="s">
+      <c r="G53" s="6" t="s">
         <v>214</v>
-      </c>
-      <c r="F53" s="6" t="s">
-        <v>215</v>
-      </c>
-      <c r="G53" s="6" t="s">
-        <v>216</v>
       </c>
       <c r="H53" s="5"/>
       <c r="I53" s="5"/>
@@ -3080,25 +3090,25 @@
     </row>
     <row r="54" spans="1:13" s="3" customFormat="1" ht="15" customHeight="1">
       <c r="A54" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="D54" s="5" t="s">
         <v>27</v>
       </c>
       <c r="E54" s="6" t="s">
+        <v>217</v>
+      </c>
+      <c r="F54" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="G54" s="6" t="s">
         <v>219</v>
-      </c>
-      <c r="F54" s="6" t="s">
-        <v>220</v>
-      </c>
-      <c r="G54" s="6" t="s">
-        <v>221</v>
       </c>
       <c r="H54" s="5"/>
       <c r="I54" s="5"/>
@@ -3109,16 +3119,16 @@
     </row>
     <row r="55" spans="1:13" s="3" customFormat="1" ht="15" customHeight="1">
       <c r="A55" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="D55" s="5" t="s">
-        <v>56</v>
+        <v>27</v>
       </c>
       <c r="E55" s="6" t="s">
         <v>222</v>
@@ -3138,25 +3148,25 @@
     </row>
     <row r="56" spans="1:13" s="3" customFormat="1" ht="15" customHeight="1">
       <c r="A56" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B56" s="5" t="s">
+        <v>220</v>
+      </c>
+      <c r="C56" s="5" t="s">
+        <v>221</v>
+      </c>
+      <c r="D56" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="E56" s="6" t="s">
         <v>225</v>
       </c>
-      <c r="C56" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="D56" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="E56" s="5" t="s">
+      <c r="F56" s="6" t="s">
         <v>226</v>
       </c>
-      <c r="F56" s="5" t="s">
+      <c r="G56" s="6" t="s">
         <v>227</v>
-      </c>
-      <c r="G56" s="6" t="s">
-        <v>228</v>
       </c>
       <c r="H56" s="5"/>
       <c r="I56" s="5"/>
@@ -3167,25 +3177,25 @@
     </row>
     <row r="57" spans="1:13" s="3" customFormat="1" ht="15" customHeight="1">
       <c r="A57" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>230</v>
+        <v>48</v>
       </c>
       <c r="D57" s="5" t="s">
         <v>27</v>
       </c>
       <c r="E57" s="5" t="s">
+        <v>229</v>
+      </c>
+      <c r="F57" s="5" t="s">
+        <v>230</v>
+      </c>
+      <c r="G57" s="6" t="s">
         <v>231</v>
-      </c>
-      <c r="F57" s="5" t="s">
-        <v>232</v>
-      </c>
-      <c r="G57" s="6" t="s">
-        <v>233</v>
       </c>
       <c r="H57" s="5"/>
       <c r="I57" s="5"/>
@@ -3194,27 +3204,27 @@
       <c r="L57" s="5"/>
       <c r="M57" s="5"/>
     </row>
-    <row r="58" spans="1:13" s="3" customFormat="1" ht="30" customHeight="1">
+    <row r="58" spans="1:13" s="3" customFormat="1" ht="15" customHeight="1">
       <c r="A58" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="C58" s="5" t="s">
-        <v>52</v>
+        <v>233</v>
       </c>
       <c r="D58" s="5" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="E58" s="5" t="s">
-        <v>199</v>
+        <v>234</v>
       </c>
       <c r="F58" s="5" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>201</v>
+        <v>236</v>
       </c>
       <c r="H58" s="5"/>
       <c r="I58" s="5"/>
@@ -3223,27 +3233,27 @@
       <c r="L58" s="5"/>
       <c r="M58" s="5"/>
     </row>
-    <row r="59" spans="1:13" s="3" customFormat="1" ht="18" customHeight="1">
+    <row r="59" spans="1:13" s="3" customFormat="1" ht="30" customHeight="1">
       <c r="A59" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="D59" s="5" t="s">
-        <v>56</v>
+        <v>31</v>
       </c>
       <c r="E59" s="5" t="s">
-        <v>110</v>
+        <v>202</v>
       </c>
       <c r="F59" s="5" t="s">
-        <v>202</v>
+        <v>237</v>
       </c>
       <c r="G59" s="6" t="s">
-        <v>235</v>
+        <v>204</v>
       </c>
       <c r="H59" s="5"/>
       <c r="I59" s="5"/>
@@ -3252,27 +3262,27 @@
       <c r="L59" s="5"/>
       <c r="M59" s="5"/>
     </row>
-    <row r="60" spans="1:13" s="3" customFormat="1" ht="34.5" customHeight="1">
+    <row r="60" spans="1:13" s="3" customFormat="1" ht="18" customHeight="1">
       <c r="A60" s="4">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="C60" s="5" t="s">
-        <v>208</v>
+        <v>21</v>
       </c>
       <c r="D60" s="5" t="s">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="E60" s="5" t="s">
-        <v>209</v>
+        <v>113</v>
       </c>
       <c r="F60" s="5" t="s">
-        <v>236</v>
+        <v>205</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="H60" s="5"/>
       <c r="I60" s="5"/>
@@ -3281,27 +3291,27 @@
       <c r="L60" s="5"/>
       <c r="M60" s="5"/>
     </row>
-    <row r="61" spans="1:13" s="3" customFormat="1" ht="27">
+    <row r="61" spans="1:13" s="3" customFormat="1" ht="34.5" customHeight="1">
       <c r="A61" s="4">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="C61" s="5" t="s">
-        <v>48</v>
+        <v>211</v>
       </c>
       <c r="D61" s="5" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="E61" s="5" t="s">
+        <v>212</v>
+      </c>
+      <c r="F61" s="5" t="s">
         <v>239</v>
       </c>
-      <c r="F61" s="5" t="s">
+      <c r="G61" s="6" t="s">
         <v>240</v>
-      </c>
-      <c r="G61" s="6" t="s">
-        <v>241</v>
       </c>
       <c r="H61" s="5"/>
       <c r="I61" s="5"/>
@@ -3310,27 +3320,27 @@
       <c r="L61" s="5"/>
       <c r="M61" s="5"/>
     </row>
-    <row r="62" spans="1:13" s="3" customFormat="1" ht="13.5">
+    <row r="62" spans="1:13" s="3" customFormat="1" ht="27">
       <c r="A62" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C62" s="5" t="s">
         <v>48</v>
       </c>
       <c r="D62" s="5" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="E62" s="5" t="s">
+        <v>242</v>
+      </c>
+      <c r="F62" s="5" t="s">
         <v>243</v>
       </c>
-      <c r="F62" s="5" t="s">
+      <c r="G62" s="6" t="s">
         <v>244</v>
-      </c>
-      <c r="G62" s="6" t="s">
-        <v>245</v>
       </c>
       <c r="H62" s="5"/>
       <c r="I62" s="5"/>
@@ -3339,27 +3349,27 @@
       <c r="L62" s="5"/>
       <c r="M62" s="5"/>
     </row>
-    <row r="63" spans="1:13" s="3" customFormat="1" ht="27">
+    <row r="63" spans="1:13" s="3" customFormat="1" ht="13.5">
       <c r="A63" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C63" s="5" t="s">
         <v>48</v>
       </c>
       <c r="D63" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="E63" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="E63" s="5" t="s">
+        <v>246</v>
+      </c>
+      <c r="F63" s="5" t="s">
         <v>247</v>
       </c>
-      <c r="F63" s="6" t="s">
+      <c r="G63" s="6" t="s">
         <v>248</v>
-      </c>
-      <c r="G63" s="6" t="s">
-        <v>249</v>
       </c>
       <c r="H63" s="5"/>
       <c r="I63" s="5"/>
@@ -3368,27 +3378,27 @@
       <c r="L63" s="5"/>
       <c r="M63" s="5"/>
     </row>
-    <row r="64" spans="1:13" s="3" customFormat="1" ht="13.5">
+    <row r="64" spans="1:13" s="3" customFormat="1" ht="27">
       <c r="A64" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C64" s="5" t="s">
-        <v>251</v>
+        <v>48</v>
       </c>
       <c r="D64" s="5" t="s">
         <v>27</v>
       </c>
       <c r="E64" s="6" t="s">
+        <v>250</v>
+      </c>
+      <c r="F64" s="6" t="s">
+        <v>251</v>
+      </c>
+      <c r="G64" s="6" t="s">
         <v>252</v>
-      </c>
-      <c r="F64" s="6" t="s">
-        <v>253</v>
-      </c>
-      <c r="G64" s="6" t="s">
-        <v>254</v>
       </c>
       <c r="H64" s="5"/>
       <c r="I64" s="5"/>
@@ -3397,17 +3407,28 @@
       <c r="L64" s="5"/>
       <c r="M64" s="5"/>
     </row>
-    <row r="65" spans="1:13" s="3" customFormat="1" ht="15" customHeight="1">
+    <row r="65" spans="1:13" s="3" customFormat="1" ht="13.5">
       <c r="A65" s="4">
-        <f>MAX($A$5:A63)+1</f>
-        <v>15</v>
-      </c>
-      <c r="B65" s="5"/>
-      <c r="C65" s="5"/>
-      <c r="D65" s="5"/>
-      <c r="E65" s="5"/>
-      <c r="F65" s="5"/>
-      <c r="G65" s="6"/>
+        <v>4</v>
+      </c>
+      <c r="B65" s="5" t="s">
+        <v>253</v>
+      </c>
+      <c r="C65" s="5" t="s">
+        <v>254</v>
+      </c>
+      <c r="D65" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="E65" s="6" t="s">
+        <v>255</v>
+      </c>
+      <c r="F65" s="6" t="s">
+        <v>256</v>
+      </c>
+      <c r="G65" s="6" t="s">
+        <v>257</v>
+      </c>
       <c r="H65" s="5"/>
       <c r="I65" s="5"/>
       <c r="J65" s="7"/>
@@ -3417,8 +3438,8 @@
     </row>
     <row r="66" spans="1:13" s="3" customFormat="1" ht="15" customHeight="1">
       <c r="A66" s="4">
-        <f>MAX($A$5:A65)+1</f>
-        <v>16</v>
+        <f>MAX($A$5:A64)+1</f>
+        <v>15</v>
       </c>
       <c r="B66" s="5"/>
       <c r="C66" s="5"/>
@@ -3436,10 +3457,10 @@
     <row r="67" spans="1:13" s="3" customFormat="1" ht="15" customHeight="1">
       <c r="A67" s="4">
         <f>MAX($A$5:A66)+1</f>
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B67" s="5"/>
-      <c r="C67" s="8"/>
+      <c r="C67" s="5"/>
       <c r="D67" s="5"/>
       <c r="E67" s="5"/>
       <c r="F67" s="5"/>
@@ -3454,10 +3475,10 @@
     <row r="68" spans="1:13" s="3" customFormat="1" ht="15" customHeight="1">
       <c r="A68" s="4">
         <f>MAX($A$5:A67)+1</f>
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B68" s="5"/>
-      <c r="C68" s="5"/>
+      <c r="C68" s="8"/>
       <c r="D68" s="5"/>
       <c r="E68" s="5"/>
       <c r="F68" s="5"/>
@@ -3472,7 +3493,7 @@
     <row r="69" spans="1:13" s="3" customFormat="1" ht="15" customHeight="1">
       <c r="A69" s="4">
         <f>MAX($A$5:A68)+1</f>
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B69" s="5"/>
       <c r="C69" s="5"/>
@@ -3490,7 +3511,7 @@
     <row r="70" spans="1:13" s="3" customFormat="1" ht="15" customHeight="1">
       <c r="A70" s="4">
         <f>MAX($A$5:A69)+1</f>
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B70" s="5"/>
       <c r="C70" s="5"/>
@@ -3508,7 +3529,7 @@
     <row r="71" spans="1:13" s="3" customFormat="1" ht="15" customHeight="1">
       <c r="A71" s="4">
         <f>MAX($A$5:A70)+1</f>
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B71" s="5"/>
       <c r="C71" s="5"/>
@@ -3526,7 +3547,7 @@
     <row r="72" spans="1:13" s="3" customFormat="1" ht="15" customHeight="1">
       <c r="A72" s="4">
         <f>MAX($A$5:A71)+1</f>
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B72" s="5"/>
       <c r="C72" s="5"/>
@@ -3544,7 +3565,7 @@
     <row r="73" spans="1:13" s="3" customFormat="1" ht="15" customHeight="1">
       <c r="A73" s="4">
         <f>MAX($A$5:A72)+1</f>
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B73" s="5"/>
       <c r="C73" s="5"/>
@@ -3562,7 +3583,7 @@
     <row r="74" spans="1:13" s="3" customFormat="1" ht="15" customHeight="1">
       <c r="A74" s="4">
         <f>MAX($A$5:A73)+1</f>
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B74" s="5"/>
       <c r="C74" s="5"/>
@@ -3580,7 +3601,7 @@
     <row r="75" spans="1:13" s="3" customFormat="1" ht="15" customHeight="1">
       <c r="A75" s="4">
         <f>MAX($A$5:A74)+1</f>
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B75" s="5"/>
       <c r="C75" s="5"/>
@@ -3598,7 +3619,7 @@
     <row r="76" spans="1:13" s="3" customFormat="1" ht="15" customHeight="1">
       <c r="A76" s="4">
         <f>MAX($A$5:A75)+1</f>
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B76" s="5"/>
       <c r="C76" s="5"/>
@@ -3616,7 +3637,7 @@
     <row r="77" spans="1:13" s="3" customFormat="1" ht="15" customHeight="1">
       <c r="A77" s="4">
         <f>MAX($A$5:A76)+1</f>
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B77" s="5"/>
       <c r="C77" s="5"/>
@@ -3634,7 +3655,7 @@
     <row r="78" spans="1:13" s="3" customFormat="1" ht="15" customHeight="1">
       <c r="A78" s="4">
         <f>MAX($A$5:A77)+1</f>
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B78" s="5"/>
       <c r="C78" s="5"/>
@@ -3652,7 +3673,7 @@
     <row r="79" spans="1:13" s="3" customFormat="1" ht="15" customHeight="1">
       <c r="A79" s="4">
         <f>MAX($A$5:A78)+1</f>
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B79" s="5"/>
       <c r="C79" s="5"/>
@@ -3667,9 +3688,27 @@
       <c r="L79" s="5"/>
       <c r="M79" s="5"/>
     </row>
-    <row r="80" spans="1:13" ht="13.5">
+    <row r="80" spans="1:13" s="3" customFormat="1" ht="15" customHeight="1">
       <c r="A80" s="4">
         <f>MAX($A$5:A79)+1</f>
+        <v>29</v>
+      </c>
+      <c r="B80" s="5"/>
+      <c r="C80" s="5"/>
+      <c r="D80" s="5"/>
+      <c r="E80" s="5"/>
+      <c r="F80" s="5"/>
+      <c r="G80" s="6"/>
+      <c r="H80" s="5"/>
+      <c r="I80" s="5"/>
+      <c r="J80" s="7"/>
+      <c r="K80" s="5"/>
+      <c r="L80" s="5"/>
+      <c r="M80" s="5"/>
+    </row>
+    <row r="81" spans="1:1" ht="13.5">
+      <c r="A81" s="4">
+        <f>MAX($A$5:A80)+1</f>
         <v>30</v>
       </c>
     </row>
@@ -3688,21 +3727,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x010100B2A485BA3BC437409D6C819718F11278" ma:contentTypeVersion="3" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="106282d7cdbab9c6795771d0b81470c2">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f91dfcdb-c723-4142-bdd9-177e27b5b094" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="d43807ce098c9a5c18372151fec5ef0e" ns2:_="">
     <xsd:import namespace="f91dfcdb-c723-4142-bdd9-177e27b5b094"/>
@@ -3840,8 +3864,23 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{24E212E4-ADE4-43F3-9F44-32B431C26D50}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2C6AEC11-C175-4CD7-B83F-9E6CA88456C9}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3849,5 +3888,5 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2C6AEC11-C175-4CD7-B83F-9E6CA88456C9}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{24E212E4-ADE4-43F3-9F44-32B431C26D50}"/>
 </file>